--- a/business_forms/049_invoice_upload_form--business_forms.xlsx
+++ b/business_forms/049_invoice_upload_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -812,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>upload_date</t>
+          <t>upload_date_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Upload Date 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -835,12 +835,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>upload_time</t>
+          <t>upload_time_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Upload Time 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -858,12 +858,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>upload_comments</t>
+          <t>upload_comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Upload Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>upload_file_type</t>
+          <t>upload_file_type_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>File Type</t>
+          <t>Upload File Type 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>uploaded_user</t>
+          <t>uploaded_user_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Upload User</t>
+          <t>Uploaded User 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1121,9 +1121,9 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'invoice',_'value':_'invoice'}</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Invoice', 'value': 'invoice'}</t>
+          <t>Invoice</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'estimate',_'value':_'estimate'}</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Estimate', 'value': 'estimate'}</t>
+          <t>Estimate</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1_mb',_'value':_1}</t>
+          <t>1_mb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1 MB', 'value': 1}</t>
+          <t>1 MB</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'5_mb',_'value':_5}</t>
+          <t>5_mb</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '5 MB', 'value': 5}</t>
+          <t>5 MB</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'10_mb',_'value':_10}</t>
+          <t>10_mb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '10 MB', 'value': 10}</t>
+          <t>10 MB</t>
         </is>
       </c>
     </row>
@@ -1321,63 +1321,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'50_mb',_'value':_50}</t>
+          <t>50_mb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '50 MB', 'value': 50}</t>
+          <t>50 MB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>upload_file_type_choices</t>
+          <t>upload_file_type_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pdf',_'value':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'PDF', 'value': 'pdf'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>upload_file_type_choices</t>
+          <t>upload_file_type_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'csv',_'value':_'csv'}</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'CSV', 'value': 'csv'}</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>upload_file_type_choices</t>
+          <t>upload_file_type_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'image',_'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Image', 'value': 'image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1406,46 +1406,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>uploaded_user_choices</t>
+          <t>uploaded_user_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>uploaded_user_choices</t>
+          <t>uploaded_user_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
